--- a/output/pdf_financials_xlsx/TGX.xlsx
+++ b/output/pdf_financials_xlsx/TGX.xlsx
@@ -6010,49 +6010,49 @@
         <v>3.091453</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>4.074226</v>
+        <v>4.32121</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>6.51181</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.798151</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>7.447311</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>9.193968999999999</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>16.221781</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>16.162421</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>16.162421</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>16.384815</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>16.740968</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>16.790896</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>16.799263</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>16.790896</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>16.719642</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>16.719642</v>
       </c>
     </row>
     <row r="93">
@@ -7475,31 +7475,31 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>1.83639</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-2.615838</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.092266</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.09779</v>
+        <v>-1.980341</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-2.143856</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.040878</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.027687</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>0.903625</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>0</v>
@@ -7508,13 +7508,13 @@
         <v>0</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.062555</v>
       </c>
       <c r="P118" s="3" t="n">
         <v>0.007445</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.025</v>
+        <v>0.0125</v>
       </c>
       <c r="R118" s="3" t="n">
         <v>0</v>
@@ -10233,7 +10233,11 @@
           <t>Reserves (note 10)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -13462,7 +13466,11 @@
           <t>Reserves (note 9(d))</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -14349,7 +14357,11 @@
           <t>Reserves (note 9(c))</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -15139,7 +15151,11 @@
           <t>Reserves (note 10(d))</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -16121,7 +16137,11 @@
           <t>Reserves (note 11(b))</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -17442,7 +17462,11 @@
           <t>Reserves (note 14(b))</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -19357,7 +19381,11 @@
           <t>Reserves (Note 13(b))</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -20367,7 +20395,11 @@
           <t>Reserves (note 12(c))</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -20969,7 +21001,11 @@
           <t>Reserves (note 11(c))</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -21476,7 +21512,11 @@
           <t>Reserves (note 10(c))</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -23526,7 +23566,11 @@
           <t>Reserves (note 10(c)) 6,511,810</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -27786,7 +27830,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -29560,7 +29608,11 @@
           <t>Impairment of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -34497,7 +34549,11 @@
           <t>Write off of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TGX.xlsx
+++ b/output/pdf_financials_xlsx/TGX.xlsx
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.07541100000000001</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002448</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.011321</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.008074</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.006991</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002716</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1110,10 +1110,10 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.001262</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.000687</v>
       </c>
     </row>
     <row r="13">
@@ -2138,16 +2138,16 @@
         <v>-3.596566</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.862961</v>
+        <v>-1.874282</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.117652</v>
+        <v>-1.125726</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.650005</v>
+        <v>-1.656996</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.370872</v>
+        <v>-1.373588</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-2.206569</v>
@@ -2174,10 +2174,10 @@
         <v>-0.276588</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.360082</v>
+        <v>-0.361344</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.326357</v>
+        <v>-0.327044</v>
       </c>
     </row>
     <row r="28">
@@ -2258,16 +2258,16 @@
         <v>-3.580439</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.849151</v>
+        <v>-1.860472</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.11093</v>
+        <v>-1.119004</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.644754</v>
+        <v>-1.651745</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.364629</v>
+        <v>-1.367345</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-2.1976</v>
@@ -2294,10 +2294,10 @@
         <v>-0.276588</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.360082</v>
+        <v>-0.361344</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.326357</v>
+        <v>-0.327044</v>
       </c>
     </row>
     <row r="30">
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.004206</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.244029</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.244029</v>
@@ -2596,19 +2596,19 @@
         <v>0.062387</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.715126</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.00326</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.019915</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.001346</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.047355</v>
       </c>
     </row>
     <row r="35">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.004206</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.244029</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.244029</v>
@@ -2712,19 +2712,19 @@
         <v>0.062387</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.066</v>
+        <v>0.781126</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.04875</v>
+        <v>0.05201</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.065</v>
+        <v>0.084915</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.06825000000000001</v>
+        <v>0.06959600000000001</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.0585</v>
+        <v>0.105855</v>
       </c>
     </row>
     <row r="37">
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.157255</v>
+        <v>0.153049</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.284321</v>
+        <v>0.040292</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.040292</v>
@@ -3408,13 +3408,13 @@
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.715126</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.00326</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.019915</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -23978,7 +23978,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
@@ -45337,7 +45337,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -45440,7 +45440,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -46628,7 +46628,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -47210,7 +47210,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -54285,7 +54285,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -55081,7 +55081,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -60756,7 +60756,7 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E527" s="5" t="n">

--- a/output/pdf_financials_xlsx/TGX.xlsx
+++ b/output/pdf_financials_xlsx/TGX.xlsx
@@ -887,40 +887,40 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.066121</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.057881</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.060783</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.11144</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>0.148993</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>0.1092</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0</v>
+        <v>0.137641</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>0.141892</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>0.128793</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>0.0072</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>0.020495</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>0</v>
@@ -954,31 +954,31 @@
         <v>1.250412</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.637613</v>
+        <v>0.749053</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.459067</v>
+        <v>0.60806</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.451259</v>
+        <v>0.560459</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.286474</v>
+        <v>0.424115</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.353386</v>
+        <v>0.495278</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.801186</v>
+        <v>0.929979</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.313008</v>
+        <v>0.320208</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.816036</v>
+        <v>0.824936</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.337183</v>
+        <v>0.357678</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.150866</v>
@@ -49819,7 +49819,11 @@
           <t>Rent and occupancy costs</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -58275,7 +58279,11 @@
           <t>Rent and occupancy costs</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E502" s="5" t="n">
         <v>0.066121</v>
       </c>

--- a/output/pdf_financials_xlsx/TGX.xlsx
+++ b/output/pdf_financials_xlsx/TGX.xlsx
@@ -771,40 +771,40 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.17143</v>
+        <v>0.20743</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.09564</v>
+        <v>0.13964</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.388184</v>
+        <v>0.441293</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.637613</v>
+        <v>0.691613</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.459067</v>
+        <v>0.5130670000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.451259</v>
+        <v>0.505259</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.286474</v>
+        <v>0.340474</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.353386</v>
+        <v>0.457386</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.801186</v>
+        <v>0.885186</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.313008</v>
+        <v>0.363708</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.816036</v>
+        <v>0.856036</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.337183</v>
+        <v>0.361857</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>0.150866</v>
@@ -954,31 +954,31 @@
         <v>1.250412</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.749053</v>
+        <v>0.803053</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.60806</v>
+        <v>0.66206</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.560459</v>
+        <v>0.614459</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.424115</v>
+        <v>0.478115</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.495278</v>
+        <v>0.599278</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.929979</v>
+        <v>1.013979</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.320208</v>
+        <v>0.370908</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.824936</v>
+        <v>0.864936</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.357678</v>
+        <v>0.382352</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.150866</v>
@@ -1365,7 +1365,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.002282</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>0.001063</v>
@@ -1374,25 +1374,25 @@
         <v>0.001219</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.02197</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.258</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1.165597</v>
+        <v>0.01976</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.014866</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>0.004075</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>-0.263906</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.429368</v>
+        <v>0.000405</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-0</v>
@@ -1610,10 +1610,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D20" s="3" t="n">
+        <v>-3.598848</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-1.861898</v>
@@ -1621,10 +1619,8 @@
       <c r="F20" s="3" t="n">
         <v>-1.116433</v>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G20" s="3" t="n">
+        <v>-1.671975</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-1.628872</v>
@@ -1632,15 +1628,11 @@
       <c r="I20" s="3" t="n">
         <v>-3.847658</v>
       </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J20" s="3" t="n">
+        <v>-1.382224</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>-1.289067</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-1.003674</v>
@@ -1655,13 +1647,13 @@
         <v>-0.887711</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-0.276588</v>
+        <v>-0.200026</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>-0.360082</v>
+        <v>-0.291189</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>-0.326357</v>
+        <v>-0.259045</v>
       </c>
     </row>
     <row r="21">
@@ -1701,25 +1693,25 @@
         <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>-0.263906</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>0.429773</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0</v>
+        <v>-0.629445</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0</v>
+        <v>-0.076561</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>-0.07656200000000001</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>0</v>
+        <v>-0.068893</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0</v>
+        <v>-0.067312</v>
       </c>
     </row>
     <row r="22">
@@ -1797,7 +1789,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-3.596566</v>
+        <v>-3.598848</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-1.861898</v>
@@ -1806,7 +1798,7 @@
         <v>-1.116433</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-1.650005</v>
+        <v>-1.671975</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-1.628872</v>
@@ -1815,10 +1807,10 @@
         <v>-3.847658</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-1.367358</v>
+        <v>-1.382224</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>-1.293142</v>
+        <v>-1.289067</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-1.26758</v>
@@ -2409,7 +2401,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.06344941257855409</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0.0570597022696664</v>
@@ -2418,25 +2410,25 @@
         <v>-0.1090679388575335</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.33151111663298</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-18.82013783927311</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-52.82395429284106</v>
+        <v>-0.8955079129635194</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.087206130362348</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.3151239384383153</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-26.29399585921325</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-126.3586628644412</v>
+        <v>-0.1191874067468901</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -6373,7 +6365,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-3.596566</v>
+        <v>-3.598848</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-1.861898</v>
@@ -6382,7 +6374,7 @@
         <v>-1.116433</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-1.650005</v>
+        <v>-1.671975</v>
       </c>
       <c r="H99" s="3" t="n">
         <v>-1.628872</v>
@@ -6391,10 +6383,10 @@
         <v>-3.847658</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>-1.367358</v>
+        <v>-1.382224</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>-1.293142</v>
+        <v>-1.289067</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-1.26758</v>
@@ -6403,19 +6395,19 @@
         <v>0.08956699999999999</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>0.171987</v>
+        <v>-0.457458</v>
       </c>
       <c r="O99" s="3" t="n">
         <v>-0.887711</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>-0.276588</v>
+        <v>-0.200026</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>-0.360082</v>
+        <v>-0.291189</v>
       </c>
       <c r="R99" s="3" t="n">
-        <v>-0.326357</v>
+        <v>-0.259045</v>
       </c>
     </row>
     <row r="100">
@@ -7298,10 +7290,10 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.03749</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.06854399999999999</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -7319,10 +7311,10 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.160838</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.089367</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -26834,7 +26826,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -28905,7 +28901,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -30681,11 +30681,7 @@
           <t>Net income (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -34167,7 +34163,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -35058,7 +35058,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -36143,7 +36147,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -41779,7 +41787,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -45745,7 +45757,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -45840,7 +45856,11 @@
           <t>Net loss from discontinued operations (note 4)</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -47414,7 +47434,11 @@
           <t>Net loss from discontinued operations (note 5)</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -48556,7 +48580,11 @@
           <t>Net income (loss) for year from discontinued operations (note 5)</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -49441,7 +49469,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -50286,7 +50318,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
@@ -50377,7 +50413,11 @@
           <t>Net income (loss) for year from discontinued operations (note 6)</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -54388,7 +54428,11 @@
           <t>Income tax recovery (expense) (note 14)</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
@@ -56798,7 +56842,11 @@
           <t>Deferred income tax recovery (expense)(note 12)</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>-</t>
@@ -57883,7 +57931,11 @@
           <t>Directors fees</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E498" s="5" t="n">
         <v>0.036</v>
       </c>
